--- a/forms/trg/Formulir_TRG_ropt.xlsx
+++ b/forms/trg/Formulir_TRG_ropt.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B34)</f>
+        <f>COUNTA(Anggota!B5:B35)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F34)</f>
+        <f>COUNTA(Anggota!F5:F35)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,20 +913,16 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Sumarni Hamid Aly, MT., IPU</t>
+          <t>Prof. Dr.Eng. Ir. Muhammad Isran Ramli, ST., MT., IPM., ASEAN Eng.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Traffic Engineering and Urban Mobility</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -946,18 +942,18 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr.Eng. Ir. Muralia Hustim, ST., MT., IPM., ASEAN Eng.</t>
+          <t>Prof. Dr. Ir. Sumarni Hamid Aly, MT., IPU</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Urban Traffic Engineering</t>
+          <t>Traffic Engineering and Urban Mobility</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -979,18 +975,18 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. M. Yahya, ST., M.Eng.</t>
+          <t>Dr.Eng. Ir. Muralia Hustim, ST., MT., IPM., ASEAN Eng.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Urban Settlement Planning</t>
+          <t>Urban Traffic Engineering</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1012,18 +1008,18 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Hajriyanti Yatmar, ST., M.Eng.</t>
+          <t>Dr. Ir. M. Yahya, ST., M.Eng.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Transportation Modeling</t>
+          <t>Urban Settlement Planning</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1045,20 +1041,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr.Eng. Ryosuke Abe</t>
+          <t>Dr. Ir. Hajriyanti Yatmar, ST., M.Eng.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Yokohama National University</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Transportation Modeling</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1078,17 +1074,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof.Ts.Dr. Muhammad Zaly Shah Muhammad Hussein</t>
+          <t>Dr.Eng. Ryosuke Abe</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>University Teknologi Malaysia</t>
+          <t>Yokohama National University</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1111,20 +1107,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ir. Raden Aisyah Nur, S.T., M.T.</t>
+          <t>Prof.Ts.Dr. Muhammad Zaly Shah Muhammad Hussein</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Urban Traffic Analysis</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>University Teknologi Malaysia</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1144,12 +1140,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Bittarae Maulana Hasbi Sjamsir, M.Sc</t>
+          <t>Ir. Raden Aisyah Nur, S.T., M.T.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1177,12 +1173,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Muntazar, S.Si., M.T.</t>
+          <t>Bittarae Maulana Hasbi Sjamsir, M.Sc</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1210,12 +1206,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Ikhsan Sabil, S.T.</t>
+          <t>Ahmad Muntazar, S.Si., M.T.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1243,18 +1239,18 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>M. Nur Wahyu Yusuf, S.T</t>
+          <t>Dr. Muhammad Ikhsan Sabil, S.T.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Master Student</t>
+          <t>Urban Traffic Analysis</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1276,18 +1272,18 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Muh. Fadel Ilhamdi</t>
+          <t>M. Nur Wahyu Yusuf, S.T</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Undergraduate Student</t>
+          <t>Master Student</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1309,12 +1305,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Adrian</t>
+          <t>Muh. Fadel Ilhamdi</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1342,12 +1338,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Yusuf</t>
+          <t>Muhammad Adrian</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1375,12 +1371,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Farhan Royani</t>
+          <t>Muhammad Yusuf</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -1408,12 +1404,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Nadya Ulya Salsabila</t>
+          <t>Muhammad Farhan Royani</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
@@ -1441,12 +1437,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Azkiyah Azzahra</t>
+          <t>Nadya Ulya Salsabila</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -1474,12 +1470,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Rizka Dwi Febriana</t>
+          <t>Azkiyah Azzahra</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
@@ -1505,10 +1501,22 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Rizka Dwi Febriana</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D23" s="12" t="n"/>
-      <c r="E23" s="11" t="n"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Undergraduate Student</t>
+        </is>
+      </c>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
@@ -1516,7 +1524,11 @@
       <c r="J23" s="12" t="n"/>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1705,15 +1717,32 @@
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="12" t="n"/>
     </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
